--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27098,6 +27098,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>1802310</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>29.7600002288818</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>27.6000003814697</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>29.6399993896484</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>28.3400001525879</v>
+      </c>
+      <c r="G1163" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27121,6 +27121,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>1113840</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>28.9400005340576</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>27.1200008392334</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>28.1200008392334</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="G1164" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27144,6 +27144,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1165">
+      <c r="A1165" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1165" t="n">
+        <v>1838790</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>27.9400005340576</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>28.6000003814697</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1165" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27167,6 +27167,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1166">
+      <c r="A1166" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1166" t="n">
+        <v>1312697</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>29.3400001525879</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>28.0200004577637</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>28.2800006866455</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>28.9799995422363</v>
+      </c>
+      <c r="G1166" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27008,22 +27008,22 @@
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1159" t="n">
-        <v>647097</v>
+        <v>735499</v>
       </c>
       <c r="C1159" t="n">
-        <v>29.0799999237061</v>
+        <v>29.5400009155273</v>
       </c>
       <c r="D1159" t="n">
-        <v>27.8999996185303</v>
+        <v>27.6599998474121</v>
       </c>
       <c r="E1159" t="n">
-        <v>28.9799995422363</v>
+        <v>27.8400001525879</v>
       </c>
       <c r="F1159" t="n">
-        <v>28.4799995422363</v>
+        <v>29.2000007629395</v>
       </c>
       <c r="G1159" t="s">
         <v>7</v>
@@ -27031,22 +27031,22 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1160" t="n">
-        <v>799558</v>
+        <v>647097</v>
       </c>
       <c r="C1160" t="n">
-        <v>29.1000003814697</v>
+        <v>29.0799999237061</v>
       </c>
       <c r="D1160" t="n">
         <v>27.8999996185303</v>
       </c>
       <c r="E1160" t="n">
-        <v>28.2600002288818</v>
+        <v>28.9799995422363</v>
       </c>
       <c r="F1160" t="n">
-        <v>28.8600006103516</v>
+        <v>28.4799995422363</v>
       </c>
       <c r="G1160" t="s">
         <v>7</v>
@@ -27054,22 +27054,22 @@
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1161" t="n">
-        <v>1172023</v>
+        <v>799558</v>
       </c>
       <c r="C1161" t="n">
-        <v>31.1000003814697</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="D1161" t="n">
-        <v>28.8199996948242</v>
+        <v>27.8999996185303</v>
       </c>
       <c r="E1161" t="n">
-        <v>29.0799999237061</v>
+        <v>28.2600002288818</v>
       </c>
       <c r="F1161" t="n">
-        <v>29.8799991607666</v>
+        <v>28.8600006103516</v>
       </c>
       <c r="G1161" t="s">
         <v>7</v>
@@ -27077,22 +27077,22 @@
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1162" t="n">
-        <v>1270516</v>
+        <v>1172023</v>
       </c>
       <c r="C1162" t="n">
-        <v>31.5799999237061</v>
+        <v>31.1000003814697</v>
       </c>
       <c r="D1162" t="n">
-        <v>29.7999992370605</v>
+        <v>28.8199996948242</v>
       </c>
       <c r="E1162" t="n">
-        <v>29.7999992370605</v>
+        <v>29.0799999237061</v>
       </c>
       <c r="F1162" t="n">
-        <v>31</v>
+        <v>29.8799991607666</v>
       </c>
       <c r="G1162" t="s">
         <v>7</v>
@@ -27100,22 +27100,22 @@
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1163" t="n">
-        <v>1802310</v>
+        <v>1270516</v>
       </c>
       <c r="C1163" t="n">
-        <v>29.7600002288818</v>
+        <v>31.5799999237061</v>
       </c>
       <c r="D1163" t="n">
-        <v>27.6000003814697</v>
+        <v>29.7999992370605</v>
       </c>
       <c r="E1163" t="n">
-        <v>29.6399993896484</v>
+        <v>29.7999992370605</v>
       </c>
       <c r="F1163" t="n">
-        <v>28.3400001525879</v>
+        <v>31</v>
       </c>
       <c r="G1163" t="s">
         <v>7</v>
@@ -27123,22 +27123,22 @@
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1164" t="n">
-        <v>1113840</v>
+        <v>1802310</v>
       </c>
       <c r="C1164" t="n">
-        <v>28.9400005340576</v>
+        <v>29.7600002288818</v>
       </c>
       <c r="D1164" t="n">
-        <v>27.1200008392334</v>
+        <v>27.6000003814697</v>
       </c>
       <c r="E1164" t="n">
-        <v>28.1200008392334</v>
+        <v>29.6399993896484</v>
       </c>
       <c r="F1164" t="n">
-        <v>28.3999996185303</v>
+        <v>28.3400001525879</v>
       </c>
       <c r="G1164" t="s">
         <v>7</v>
@@ -27146,22 +27146,22 @@
     </row>
     <row r="1165">
       <c r="A1165" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1165" t="n">
-        <v>1838790</v>
+        <v>1113840</v>
       </c>
       <c r="C1165" t="n">
-        <v>29.1000003814697</v>
+        <v>28.9400005340576</v>
       </c>
       <c r="D1165" t="n">
-        <v>27.9400005340576</v>
+        <v>27.1200008392334</v>
       </c>
       <c r="E1165" t="n">
-        <v>28.6000003814697</v>
+        <v>28.1200008392334</v>
       </c>
       <c r="F1165" t="n">
-        <v>28</v>
+        <v>28.3999996185303</v>
       </c>
       <c r="G1165" t="s">
         <v>7</v>
@@ -27169,24 +27169,47 @@
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1166" t="n">
-        <v>1312697</v>
+        <v>1838790</v>
       </c>
       <c r="C1166" t="n">
-        <v>29.3400001525879</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="D1166" t="n">
-        <v>28.0200004577637</v>
+        <v>27.9400005340576</v>
       </c>
       <c r="E1166" t="n">
-        <v>28.2800006866455</v>
+        <v>28.6000003814697</v>
       </c>
       <c r="F1166" t="n">
-        <v>28.9799995422363</v>
+        <v>28</v>
       </c>
       <c r="G1166" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>6501915</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>29.4599990844727</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>28.2000007629395</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>29.2000007629395</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>29.4599990844727</v>
+      </c>
+      <c r="G1167" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -30769,6 +30769,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>1612218</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>31.5799999237061</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>29.8999996185303</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>31.2600002288818</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>30.8199996948242</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>30.8199996948242</v>
+      </c>
+      <c r="H1170" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -30795,6 +30795,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>1111227</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>31.5599994659424</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>30.6599998474121</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>30.9200000762939</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>30.9799995422363</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>30.9799995422363</v>
+      </c>
+      <c r="H1171" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -30821,6 +30821,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>818088</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>30.7999992370605</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>29.4400005340576</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>30.7999992370605</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>29.4799995422363</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>29.4799995422363</v>
+      </c>
+      <c r="H1172" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -30847,6 +30847,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>753783</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>30.8799991607666</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>29.7999992370605</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>30.1399993896484</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>30.1399993896484</v>
+      </c>
+      <c r="H1173" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -30925,6 +30925,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>1740379</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>33.9199981689453</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>32.0200004577637</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>32.1599998474121</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>33.0200004577637</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>33.0200004577637</v>
+      </c>
+      <c r="H1176" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27482,8 +27482,31 @@
       <c r="E1179" t="n">
         <v>35.5</v>
       </c>
-      <c r="F1179"/>
+      <c r="F1179" t="n">
+        <v>35.8400001525879</v>
+      </c>
       <c r="G1179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>2066454</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>37.8800010681152</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>36.3800010681152</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>36.4599990844727</v>
+      </c>
+      <c r="F1180"/>
+      <c r="G1180" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27505,8 +27505,31 @@
       <c r="E1180" t="n">
         <v>36.4599990844727</v>
       </c>
-      <c r="F1180"/>
+      <c r="F1180" t="n">
+        <v>36.8400001525879</v>
+      </c>
       <c r="G1180" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>2065425</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>36.6399993896484</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>33.939998626709</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>36.5999984741211</v>
+      </c>
+      <c r="F1181"/>
+      <c r="G1181" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27528,8 +27528,31 @@
       <c r="E1181" t="n">
         <v>36.5999984741211</v>
       </c>
-      <c r="F1181"/>
+      <c r="F1181" t="n">
+        <v>34.6399993896484</v>
+      </c>
       <c r="G1181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>1490534</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>34.2799987792969</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>33.4199981689453</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>34.0800018310547</v>
+      </c>
+      <c r="F1182"/>
+      <c r="G1182" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27551,8 +27551,31 @@
       <c r="E1182" t="n">
         <v>34.0800018310547</v>
       </c>
-      <c r="F1182"/>
+      <c r="F1182" t="n">
+        <v>33.8400001525879</v>
+      </c>
       <c r="G1182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>1532462</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>35.1800003051758</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>33.7200012207031</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>33.9199981689453</v>
+      </c>
+      <c r="F1183"/>
+      <c r="G1183" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -27581,6 +27581,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1184" t="n">
+        <v>897382</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>34.3400001525879</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>33.1399993896484</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>33.9599990844727</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>33.3199996948242</v>
+      </c>
+      <c r="G1184" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -31211,6 +31211,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>3635565</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>26.9400005340576</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>27.9599990844727</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>27.9599990844727</v>
+      </c>
+      <c r="H1187" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -31216,7 +31216,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B1187" t="n">
-        <v>3635565</v>
+        <v>3652065</v>
       </c>
       <c r="C1187" t="n">
         <v>29.5</v>
@@ -31234,6 +31234,32 @@
         <v>27.9599990844727</v>
       </c>
       <c r="H1187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>2421358</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>28.7600002288818</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>26.4599990844727</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>28.6000003814697</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>26.5200004577637</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>26.5200004577637</v>
+      </c>
+      <c r="H1188" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -34830,6 +34830,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1189">
+      <c r="A1189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1189" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>26.8799991607666</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>27.2000007629395</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>26.0400009155273</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>26.8199996948242</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>26.8199996948242</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>1884930</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1190" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>26.0799999237061</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>26.8799991607666</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>25.5400009155273</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>26.0200004577637</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>26.0200004577637</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>1710487</v>
+      </c>
+      <c r="I1190" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -34888,6 +34888,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1191">
+      <c r="A1191" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1191" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>26.5799999237061</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>27.0400009155273</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>26.1000003814697</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>26.7399997711182</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>26.7399997711182</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>1904058</v>
+      </c>
+      <c r="I1191" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -34917,6 +34917,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1192">
+      <c r="A1192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1192" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>25.6599998474121</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>25.8400001525879</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>24.5799999237061</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>1836390</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -34946,6 +34946,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1193" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>24.9599990844727</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>23.6800003051758</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>23.6800003051758</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>1700043</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -34975,6 +34975,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1194" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>23.6399993896484</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>25.4200000762939</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>1639212</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -35004,6 +35004,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1195">
+      <c r="A1195" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1195" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>25.9599990844727</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>24.9599990844727</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>25.8400001525879</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>25.8400001525879</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>1484533</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -35033,6 +35033,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1196">
+      <c r="A1196" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1196" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>26.7800006866455</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>26.1200008392334</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>26.2800006866455</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>26.2800006866455</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>1444514</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -35062,6 +35062,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1197" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>25.9799995422363</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>27.1200008392334</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>25.8799991607666</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>1348143</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TPRO.MI.xlsx
+++ b/data/TPRO.MI.xlsx
@@ -35091,6 +35091,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1198" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>25.5200004577637</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>25.5200004577637</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>24.0200004577637</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>24.2199993133545</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>24.2199993133545</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>2389154</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
